--- a/data/trans_dic/Q17F_D_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 18,23</t>
+          <t>6,23; 18,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 18,61</t>
+          <t>8,13; 17,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 17,72</t>
+          <t>7,47; 16,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 18,22</t>
+          <t>6,61; 17,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,33</t>
+          <t>3,23; 10,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,09</t>
+          <t>5,81; 13,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 17,77</t>
+          <t>8,49; 17,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 18,5</t>
+          <t>9,92; 18,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,2</t>
+          <t>5,65; 11,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,88</t>
+          <t>7,82; 14,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 15,57</t>
+          <t>9,12; 15,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 16,27</t>
+          <t>9,84; 16,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,39</t>
+          <t>4,07; 12,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 18,21</t>
+          <t>8,08; 17,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,65</t>
+          <t>5,03; 12,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 19,92</t>
+          <t>9,86; 20,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,52</t>
+          <t>6,03; 13,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 12,93</t>
+          <t>6,4; 12,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,44</t>
+          <t>5,16; 11,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,56</t>
+          <t>13,53; 21,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,48</t>
+          <t>6,14; 11,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,2</t>
+          <t>7,87; 13,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,33</t>
+          <t>5,66; 10,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,35</t>
+          <t>12,73; 19,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 25,42</t>
+          <t>12,16; 26,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 21,18</t>
+          <t>8,7; 20,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 23,23</t>
+          <t>10,7; 24,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 34,0</t>
+          <t>17,7; 35,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,77</t>
+          <t>10,48; 21,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 17,04</t>
+          <t>7,91; 16,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 24,82</t>
+          <t>14,53; 24,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 30,19</t>
+          <t>17,74; 30,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 20,14</t>
+          <t>12,63; 20,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 16,57</t>
+          <t>9,12; 16,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 22,47</t>
+          <t>14,33; 22,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 30,03</t>
+          <t>19,98; 30,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 18,03</t>
+          <t>8,76; 17,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,33</t>
+          <t>7,6; 18,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,41</t>
+          <t>5,66; 13,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 27,78</t>
+          <t>16,47; 27,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,79</t>
+          <t>8,99; 16,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,68</t>
+          <t>8,56; 16,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 17,4</t>
+          <t>9,01; 17,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 25,46</t>
+          <t>10,14; 25,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,67</t>
+          <t>9,45; 15,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,33</t>
+          <t>9,21; 15,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 14,3</t>
+          <t>8,26; 14,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 24,01</t>
+          <t>13,34; 24,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,89</t>
+          <t>9,76; 15,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,16</t>
+          <t>10,09; 15,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,39</t>
+          <t>8,56; 13,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,37</t>
+          <t>15,55; 21,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,79</t>
+          <t>8,64; 12,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,44</t>
+          <t>8,78; 12,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 14,64</t>
+          <t>10,52; 14,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 21,22</t>
+          <t>13,77; 21,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,96</t>
+          <t>9,77; 12,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,12</t>
+          <t>9,8; 12,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 13,43</t>
+          <t>10,43; 13,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,51; 20,45</t>
+          <t>15,62; 20,42</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6986; 20369</t>
+          <t>6961; 21004</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14793; 32717</t>
+          <t>14295; 31613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14171; 31929</t>
+          <t>13449; 30118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6981; 19820</t>
+          <t>7192; 18854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6129; 19086</t>
+          <t>5978; 19442</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13468; 31387</t>
+          <t>12950; 30725</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20242; 40319</t>
+          <t>19264; 39427</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15775; 29277</t>
+          <t>15701; 29851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17189; 36173</t>
+          <t>16757; 35235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30820; 55326</t>
+          <t>31148; 56964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36251; 63389</t>
+          <t>37099; 62712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25275; 43443</t>
+          <t>26294; 44579</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7235; 21479</t>
+          <t>7056; 21309</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19087; 40467</t>
+          <t>17948; 38138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13216; 32523</t>
+          <t>12931; 31936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16754; 34293</t>
+          <t>16979; 35207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17203; 38545</t>
+          <t>17189; 37840</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22026; 45032</t>
+          <t>22289; 43614</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17538; 39167</t>
+          <t>17651; 39125</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26728; 43933</t>
+          <t>27574; 44423</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27950; 52628</t>
+          <t>28154; 53225</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45831; 75319</t>
+          <t>44881; 75293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35287; 61926</t>
+          <t>33923; 62044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48184; 72743</t>
+          <t>47853; 72744</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15971; 34602</t>
+          <t>16546; 36056</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14655; 34797</t>
+          <t>14290; 34244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17049; 38692</t>
+          <t>17828; 40497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22546; 41939</t>
+          <t>21832; 43175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20246; 40252</t>
+          <t>20315; 40987</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15528; 35981</t>
+          <t>16712; 35242</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33881; 59797</t>
+          <t>35013; 59532</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26181; 43203</t>
+          <t>25384; 43151</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40285; 66435</t>
+          <t>41676; 67902</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35520; 62210</t>
+          <t>34253; 62562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59284; 91569</t>
+          <t>58393; 90917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52739; 80011</t>
+          <t>53237; 80914</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16277; 33158</t>
+          <t>16109; 32690</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14557; 33668</t>
+          <t>13962; 34433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12648; 28491</t>
+          <t>12016; 29259</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32332; 56127</t>
+          <t>33280; 55036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26660; 51137</t>
+          <t>27377; 51669</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27482; 51074</t>
+          <t>27894; 52424</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27620; 51707</t>
+          <t>26772; 51271</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35425; 88147</t>
+          <t>35102; 88109</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47090; 76536</t>
+          <t>46157; 77584</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47755; 78092</t>
+          <t>46942; 77932</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43261; 72848</t>
+          <t>42088; 73279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70193; 131627</t>
+          <t>73141; 134127</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59288; 90084</t>
+          <t>59039; 90940</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75938; 113125</t>
+          <t>75237; 113769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71659; 109319</t>
+          <t>69880; 108106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92863; 129600</t>
+          <t>94283; 131578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>85481; 123824</t>
+          <t>83660; 124655</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95519; 137801</t>
+          <t>97245; 138518</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>118387; 162123</t>
+          <t>116471; 161563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121737; 180635</t>
+          <t>117282; 181987</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153636; 203874</t>
+          <t>153644; 203563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>184530; 243251</t>
+          <t>181779; 238738</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196733; 258302</t>
+          <t>200623; 260124</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>226106; 298147</t>
+          <t>227705; 297678</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q17F_D_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,8</t>
+          <t>6,17; 18,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,99</t>
+          <t>7,9; 18,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,72</t>
+          <t>7,64; 17,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 17,33</t>
+          <t>6,47; 19,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,52</t>
+          <t>3,54; 10,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 13,8</t>
+          <t>5,95; 13,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,38</t>
+          <t>8,42; 17,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,86</t>
+          <t>10,29; 18,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,88</t>
+          <t>5,36; 11,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,3</t>
+          <t>7,59; 13,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 15,41</t>
+          <t>9,31; 15,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,69</t>
+          <t>9,93; 16,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 12,29</t>
+          <t>4,07; 12,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 17,16</t>
+          <t>8,14; 16,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,42</t>
+          <t>5,25; 12,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 20,45</t>
+          <t>10,29; 20,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,28</t>
+          <t>5,7; 12,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,52</t>
+          <t>6,41; 13,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,43</t>
+          <t>5,35; 11,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 21,8</t>
+          <t>13,14; 21,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,61</t>
+          <t>5,95; 11,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 13,2</t>
+          <t>7,98; 13,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,35</t>
+          <t>5,85; 10,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,35</t>
+          <t>13,12; 19,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 26,49</t>
+          <t>11,6; 26,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 20,84</t>
+          <t>9,06; 20,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 24,31</t>
+          <t>10,84; 24,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,7; 35,0</t>
+          <t>17,43; 32,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 21,15</t>
+          <t>10,6; 20,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 16,69</t>
+          <t>7,94; 17,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 24,71</t>
+          <t>14,33; 25,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 30,15</t>
+          <t>18,72; 30,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,63; 20,58</t>
+          <t>12,32; 20,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 16,66</t>
+          <t>9,49; 16,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 22,31</t>
+          <t>14,54; 22,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,98; 30,37</t>
+          <t>19,87; 29,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,78</t>
+          <t>8,89; 17,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,75</t>
+          <t>7,78; 18,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,77</t>
+          <t>5,4; 13,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 27,24</t>
+          <t>17,08; 28,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,96</t>
+          <t>8,79; 16,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 16,09</t>
+          <t>8,43; 15,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,26</t>
+          <t>9,18; 17,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 25,44</t>
+          <t>20,63; 29,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,88</t>
+          <t>9,66; 15,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 15,3</t>
+          <t>9,31; 15,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,38</t>
+          <t>8,53; 14,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 24,46</t>
+          <t>20,13; 27,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,03</t>
+          <t>9,69; 15,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,25</t>
+          <t>10,15; 15,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,24</t>
+          <t>8,61; 13,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 21,7</t>
+          <t>15,78; 21,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,87</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,5</t>
+          <t>8,94; 12,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,59</t>
+          <t>10,61; 14,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,37</t>
+          <t>18,33; 22,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 12,94</t>
+          <t>9,88; 13,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,88</t>
+          <t>9,92; 12,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,52</t>
+          <t>10,31; 13,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,42</t>
+          <t>17,89; 21,58</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>37116</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6961; 21004</t>
+          <t>6892; 20446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14295; 31613</t>
+          <t>13892; 31850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13449; 30118</t>
+          <t>13763; 31299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7192; 18854</t>
+          <t>7442; 21944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5978; 19442</t>
+          <t>6535; 19441</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12950; 30725</t>
+          <t>13244; 30918</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19264; 39427</t>
+          <t>19093; 39291</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15701; 29851</t>
+          <t>17387; 32047</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16757; 35235</t>
+          <t>15909; 35286</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31148; 56964</t>
+          <t>30249; 54131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37099; 62712</t>
+          <t>37885; 62994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26294; 44579</t>
+          <t>28225; 46868</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>67336</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7056; 21309</t>
+          <t>7061; 21443</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17948; 38138</t>
+          <t>18081; 37643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12931; 31936</t>
+          <t>13505; 32520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16979; 35207</t>
+          <t>19692; 40192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17189; 37840</t>
+          <t>16243; 36496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22289; 43614</t>
+          <t>22326; 45568</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17651; 39125</t>
+          <t>18321; 39397</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27574; 44423</t>
+          <t>30505; 49154</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28154; 53225</t>
+          <t>27265; 52250</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44881; 75293</t>
+          <t>45524; 74422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33923; 62044</t>
+          <t>35073; 61744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47853; 72744</t>
+          <t>55579; 83259</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>33269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>74338</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16546; 36056</t>
+          <t>15784; 35941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14290; 34244</t>
+          <t>14896; 33601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17828; 40497</t>
+          <t>18051; 40094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21832; 43175</t>
+          <t>23468; 44327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20315; 40987</t>
+          <t>20540; 39080</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16712; 35242</t>
+          <t>16770; 37097</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35013; 59532</t>
+          <t>34513; 60358</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25384; 43151</t>
+          <t>31952; 51540</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41676; 67902</t>
+          <t>40657; 68897</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34253; 62562</t>
+          <t>35627; 63501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58393; 90917</t>
+          <t>59244; 92364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53237; 80914</t>
+          <t>60658; 88824</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42520</t>
+          <t>45873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>120458</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16109; 32690</t>
+          <t>16352; 32916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13962; 34433</t>
+          <t>14291; 33935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12016; 29259</t>
+          <t>11473; 27969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33280; 55036</t>
+          <t>35950; 59446</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27377; 51669</t>
+          <t>26765; 51382</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27894; 52424</t>
+          <t>27457; 50182</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26772; 51271</t>
+          <t>27286; 52171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35102; 88109</t>
+          <t>62249; 88141</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46157; 77584</t>
+          <t>47163; 75997</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46942; 77932</t>
+          <t>47458; 77439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42088; 73279</t>
+          <t>43469; 72635</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73141; 134127</t>
+          <t>103126; 138701</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>120965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>299248</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59039; 90940</t>
+          <t>58656; 91638</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75237; 113769</t>
+          <t>75691; 113651</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69880; 108106</t>
+          <t>70285; 107819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94283; 131578</t>
+          <t>102826; 142922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83660; 124655</t>
+          <t>84711; 124464</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97245; 138518</t>
+          <t>99034; 139149</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>116471; 161563</t>
+          <t>117428; 164343</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117282; 181987</t>
+          <t>160135; 200627</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153644; 203563</t>
+          <t>155508; 205889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181779; 238738</t>
+          <t>183941; 239724</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200623; 260124</t>
+          <t>198395; 257585</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>227705; 297678</t>
+          <t>272816; 329167</t>
         </is>
       </c>
     </row>
